--- a/weather.xlsx
+++ b/weather.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,156 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1021</v>
+      </c>
+      <c r="F4" t="n">
+        <v>63</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:19:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1021</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1021</v>
+      </c>
+      <c r="F6" t="n">
+        <v>63</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:20:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1021</v>
+      </c>
+      <c r="F7" t="n">
+        <v>63</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:20:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1021</v>
+      </c>
+      <c r="F8" t="n">
+        <v>63</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:20:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
